--- a/output/2026-09-03_12_Italia_Campania_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-03_12_Italia_Campania_Utensilerie_e_Macchine_Utensili.xlsx
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Via Colonnello Gabriele Pepe 30, Napoli. Forniture industriali, antinfortunistica, trasmissioni industriali. Sito web non trovato/verificabile.</t>
+          <t>Via Colonnello Gabriele Pepe 30, Napoli. Forniture industriali, antinfortunistica, trasmissioni industriali. Sito web non trovato/verificabile. [DUPLICATO — vedi anche: 2026-09-03_04_Italia_Campania_Componentistica-Ventilazione-industriale.xlsx]</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Via S. Cosmo Fuori Porta Nolana 99, Napoli. Forniture industriali. Sito web non trovato/verificabile.</t>
+          <t>Via S. Cosmo Fuori Porta Nolana 99, Napoli. Forniture industriali. Sito web non trovato/verificabile. [DUPLICATO — vedi anche: 2026-09-03_04_Italia_Campania_Componentistica-Ventilazione-industriale.xlsx]</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
